--- a/rules/CORE-001080/positive/01/data/unit-test-coreid-CG0288-positive 1.xlsx
+++ b/rules/CORE-001080/positive/01/data/unit-test-coreid-CG0288-positive 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdisc.sharepoint.com/sites/CORERules/Shared Documents/unitTesting/SDTMIG/CG0288/positive/01/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-001080\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{39787DBA-5238-4264-8444-50AED7FA4F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{459B29BF-AA4C-4418-B5F8-8631AD9FACD9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517C041F-6FFC-4CB8-AA85-D2FB249EFFBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="858" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="91" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="200">
   <si>
     <t>Filename</t>
   </si>
@@ -632,6 +632,12 @@
   </si>
   <si>
     <t>2025-03-28</t>
+  </si>
+  <si>
+    <t>CISC</t>
+  </si>
+  <si>
+    <t>C00001</t>
   </si>
 </sst>
 </file>
@@ -1322,10 +1328,10 @@
         <v>35</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>36</v>
+        <v>199</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>37</v>
+        <v>198</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>197</v>
@@ -2565,25 +2571,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090ADB40D834AE945B19FCDA4041AC0CB" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d36826f407302d9fd93d8089214679b0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xmlns:ns3="63ea592b-d684-45c7-8cdc-fad8f8e6bb41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="257daeb82d9c284d9d656fb5e9ad601e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -2823,10 +2810,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBA1534A-10C2-489F-9705-E7B5AAFDDEEC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1DC2495-E438-4A44-957D-A68919CCA0BC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+    <ds:schemaRef ds:uri="63ea592b-d684-45c7-8cdc-fad8f8e6bb41"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2844,10 +2862,15 @@
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1DC2495-E438-4A44-957D-A68919CCA0BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBA1534A-10C2-489F-9705-E7B5AAFDDEEC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>